--- a/artfynd/A 45053-2024 artfynd.xlsx
+++ b/artfynd/A 45053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150367</v>
+        <v>121150368</v>
       </c>
       <c r="B2" t="n">
-        <v>91127</v>
+        <v>91453</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533787</v>
+        <v>534156</v>
       </c>
       <c r="R2" t="n">
-        <v>6612586</v>
+        <v>6612026</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150368</v>
+        <v>121150367</v>
       </c>
       <c r="B3" t="n">
-        <v>91443</v>
+        <v>91137</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534156</v>
+        <v>533787</v>
       </c>
       <c r="R3" t="n">
-        <v>6612026</v>
+        <v>6612586</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 45053-2024 artfynd.xlsx
+++ b/artfynd/A 45053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150368</v>
       </c>
       <c r="B2" t="n">
-        <v>91453</v>
+        <v>91465</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150367</v>
       </c>
       <c r="B3" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 45053-2024 artfynd.xlsx
+++ b/artfynd/A 45053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150368</v>
+        <v>121150367</v>
       </c>
       <c r="B2" t="n">
-        <v>91465</v>
+        <v>91150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534156</v>
+        <v>533787</v>
       </c>
       <c r="R2" t="n">
-        <v>6612026</v>
+        <v>6612586</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150367</v>
+        <v>121150368</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91466</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533787</v>
+        <v>534156</v>
       </c>
       <c r="R3" t="n">
-        <v>6612586</v>
+        <v>6612026</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 45053-2024 artfynd.xlsx
+++ b/artfynd/A 45053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150367</v>
       </c>
       <c r="B2" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150368</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>91469</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
